--- a/ai-training-prompt-engineering/deliverables/Course_Workbook.xlsx
+++ b/ai-training-prompt-engineering/deliverables/Course_Workbook.xlsx
@@ -14190,7 +14190,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Source: Packaging_Change_Thread.txt (paste it into any approved assistant). Native path, verified Sep 2026 (notes/research/r28): Outlook's "Summary by Copilot" on an open thread, with numbered citations — availability depends on your organization's Copilot license, and the pasted-text version always works. Never practice on real confidential threads.</t>
+          <t>Source: Packaging_Change_Thread.txt (paste it into any approved assistant). Native path, verified Sep 2026 (notes/research/r28): open the thread in Outlook and use "Summary by Copilot" (numbered citations); then run THE PROMPT ABOVE in the Copilot chat pane, scoped to that same conversation — that is where the custom prompt goes after the built-in summary. Availability depends on your organization's Copilot license; the fallback that always works is pasting Packaging_Change_Thread.txt with the same prompt into any approved assistant. Never practice on real confidential threads.</t>
         </is>
       </c>
       <c r="C8" s="2" t="n"/>

--- a/ai-training-prompt-engineering/deliverables/Course_Workbook.xlsx
+++ b/ai-training-prompt-engineering/deliverables/Course_Workbook.xlsx
@@ -6950,7 +6950,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Working only on the 144 data rows (exclude the TOTAL row; treat the "n/a" as missing and say so): 1) Which supplier has the highest defect rate — (Defects_Found + Units_Returned) / Units_Shipped — overall, and is it getting better or worse across the year? 2) Is there a relationship between Inspection_Hours and Units_Returned? Compute the correlation by running code, show your working, and describe it as an association, not a cause. 3) Rank the sites by On_Time_Percent. Answer in that order, then stop.</t>
+          <t>Working only on the 144 data rows (exclude the TOTAL row; treat the "n/a" as missing and say so): 1) Which supplier has the highest defect rate — Defects_Found ÷ Units_Shipped; returns are a separate measure, never added — overall, and is it getting better or worse across the year? 2) Is there a relationship between Inspection_Hours and Units_Returned? Compute the correlation by running code, show your working, and describe it as an association, not a cause. 3) Rank the sites by On_Time_Percent. Answer in that order, then stop.</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -7441,7 +7441,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Named columns, exact arithmetic — e.g. defect rate = (Defects_Found + Units_Returned) / Units_Shipped. If you can't write the formula, you can't track the number.</t>
+          <t>Named columns, exact arithmetic — e.g. defect rate = Defects_Found ÷ Units_Shipped (returns are a separate measure — never add the two). If you can't write the formula, you can't track the number.</t>
         </is>
       </c>
       <c r="C13" s="2" t="n"/>

--- a/ai-training-prompt-engineering/deliverables/Course_Workbook.xlsx
+++ b/ai-training-prompt-engineering/deliverables/Course_Workbook.xlsx
@@ -8050,7 +8050,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Anthropic 2026 · Yang 2026: unstated requirements guessed right only 41.1%</t>
+          <t>Anthropic 2026 · Yang et al., 2025; revised 2026: unstated requirements guessed right only 41.1%</t>
         </is>
       </c>
     </row>
